--- a/03_Outputs/all/01_TablasDescriptivas/idx5_viviendas_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx5_viviendas_vr.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.229275229564136</v>
+        <v>2.229275229564134</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.331650612496902</v>
+        <v>1.331650612496903</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9641303496876992</v>
+        <v>0.9641303496876987</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.7848047881187857</v>
+        <v>0.7848047881187854</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.4855748608876544</v>
+        <v>0.4855748608876546</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.2045641592448237</v>
+        <v>0.2045641592448242</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>2.229275229564136</v>
+        <v>2.229275229564134</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>3.560925842061037</v>
+        <v>3.560925842061038</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>4.525056191748737</v>
+        <v>4.525056191748736</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>5.309860979867523</v>
+        <v>5.309860979867522</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.795435840755177</v>
+        <v>5.795435840755176</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>37.15458715940225</v>
+        <v>37.15458715940223</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>22.19417687494836</v>
+        <v>22.19417687494839</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>16.06883916146165</v>
+        <v>16.06883916146164</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>8.092914348127572</v>
+        <v>8.092914348127575</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>3.409402654080393</v>
+        <v>3.409402654080403</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>37.15458715940225</v>
+        <v>37.15458715940223</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>75.41760319581228</v>
+        <v>75.41760319581226</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>88.49768299779203</v>
+        <v>88.49768299779201</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>96.5905973459196</v>
+        <v>96.59059734591958</v>
       </c>
       <c r="C24">
         <v>5</v>
